--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NATIORA\Desktop\S6\MrRojo\TP\SEO\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B7C0AE-67FE-4EB3-8F73-CDAB5A81539A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F308CAA8-6EDA-4DC8-9DE8-0AD6ACA3BA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>ETU003252</t>
   </si>
@@ -161,14 +161,44 @@
   <si>
     <t>Structuration</t>
   </si>
+  <si>
+    <t>Authentification</t>
+  </si>
+  <si>
+    <t>metier</t>
+  </si>
+  <si>
+    <t>Bakc-office</t>
+  </si>
+  <si>
+    <t>Back-office</t>
+  </si>
+  <si>
+    <t>Inscription dans le site new</t>
+  </si>
+  <si>
+    <t>SignIn.php</t>
+  </si>
+  <si>
+    <t>connexion dans le site new</t>
+  </si>
+  <si>
+    <t>Login.php</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>Mettre en place le système d'authentifiaction</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="d/m"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="d/m"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -270,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -353,24 +383,6 @@
         <color rgb="FF999999"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
       <top style="thin">
         <color rgb="FF999999"/>
       </top>
@@ -407,11 +419,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -443,7 +455,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -452,17 +464,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,7 +709,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="NATIORA" refreshedDate="46109.930036458332" refreshedVersion="8" recordCount="83" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="NATIORA" refreshedDate="46110.462507523145" refreshedVersion="8" recordCount="83" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K84" sheet="liste des taches"/>
   </cacheSource>
@@ -716,30 +724,30 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Page" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Type" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Qui" numFmtId="0">
       <sharedItems containsBlank="1" count="5">
-        <s v="ETU003777"/>
         <s v="ETU003252"/>
         <m/>
+        <s v="ETU003777" u="1"/>
         <s v="ETU003329" u="1"/>
         <s v="ETU003289" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Estimation" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="90"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="90"/>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="90"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="90"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="Avancement" numFmtId="169">
+    <cacheField name="Avancement" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
   </cacheFields>
@@ -754,24 +762,168 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="83">
   <r>
-    <s v="infrastructure"/>
-    <s v="Docker"/>
-    <s v="docker-compose"/>
+    <s v="Conception"/>
+    <s v="Base de donnee"/>
+    <s v="faire la conception du projet"/>
+    <m/>
+    <s v="BDD"/>
+    <x v="0"/>
+    <n v="40"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Structuration"/>
+    <s v="Core"/>
+    <s v="mettre en place le strucutre du projet"/>
     <m/>
     <s v="setup"/>
     <x v="0"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="orchestration"/>
+    <s v="Docker"/>
+    <s v="mettre l'environement Docker"/>
+    <s v="docker-file/docker-yml"/>
+    <s v="setup"/>
+    <x v="0"/>
+    <n v="25"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
     <n v="60"/>
     <n v="60"/>
     <n v="0"/>
     <n v="1"/>
   </r>
   <r>
-    <s v="infrastructure"/>
-    <s v="Docker"/>
-    <s v="server carte dans docker offliene(Tanà)"/>
-    <m/>
-    <s v="setup"/>
-    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
     <n v="60"/>
     <n v="60"/>
     <n v="0"/>
@@ -784,8 +936,8 @@
     <m/>
     <m/>
     <x v="1"/>
-    <n v="5"/>
-    <n v="5"/>
+    <n v="60"/>
+    <n v="60"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -795,7 +947,535 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="35"/>
+    <n v="35"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="50"/>
+    <n v="50"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
     <n v="15"/>
     <n v="15"/>
     <n v="0"/>
@@ -807,7 +1487,211 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="65"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
     <n v="15"/>
     <n v="15"/>
     <n v="0"/>
@@ -819,9 +1703,9 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
-    <n v="15"/>
-    <n v="15"/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="60"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -831,7 +1715,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -843,7 +1727,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -855,7 +1739,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -867,883 +1751,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="20"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="35"/>
-    <n v="35"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="50"/>
-    <n v="50"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="45"/>
-    <n v="45"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="45"/>
-    <n v="45"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="45"/>
-    <n v="45"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="20"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="15"/>
-    <n v="15"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="20"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="20"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="65"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="15"/>
-    <n v="15"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
+    <x v="1"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1754,7 +1762,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="" updatedVersion="8" compact="0" compactData="0">
-  <location ref="A1:D5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="A1:D4" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -1763,28 +1771,25 @@
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items count="6">
-        <item x="1"/>
+        <item x="0"/>
         <item h="1" m="1" x="4"/>
         <item h="1" m="1" x="3"/>
-        <item x="0"/>
-        <item h="1" x="2"/>
+        <item m="1" x="2"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField compact="0" numFmtId="169" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="2">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -3206,75 +3211,111 @@
       <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H5" s="18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5" s="18">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J5" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K5" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H6" s="18">
         <v>15</v>
       </c>
       <c r="I6" s="18">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J6" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K6" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H7" s="18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I7" s="18">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K7" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
@@ -6159,44 +6200,31 @@
       <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28">
-        <v>5</v>
-      </c>
-      <c r="C3" s="29">
-        <v>5</v>
-      </c>
-      <c r="D3" s="30">
+      <c r="B3" s="29">
+        <v>95</v>
+      </c>
+      <c r="C3" s="30">
+        <v>95</v>
+      </c>
+      <c r="D3" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>2</v>
+      <c r="A4" s="28" t="s">
+        <v>29</v>
       </c>
       <c r="B4" s="32">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C4" s="33">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D4" s="34">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="36">
-        <v>125</v>
-      </c>
-      <c r="C5" s="37">
-        <v>125</v>
-      </c>
-      <c r="D5" s="38">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="6" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="7" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="8" spans="1:4" ht="15.75" customHeight="1"/>
@@ -6209,7 +6237,7 @@
       </c>
       <c r="B12" s="15">
         <f>avancement!D2</f>
-        <v>1</v>
+        <v>0.98461538461538467</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7242,23 +7270,23 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="10">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>3560</v>
+        <v>3570</v>
       </c>
       <c r="B2" s="10">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>3565</v>
+        <v>3520</v>
       </c>
       <c r="C2" s="10">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D2" s="11">
         <f>(B2/(B2+C2))</f>
-        <v>1</v>
+        <v>0.98461538461538467</v>
       </c>
       <c r="E2" s="11">
         <f>((B2+C2)-A2)/A2</f>
-        <v>1.4044943820224719E-3</v>
+        <v>1.4005602240896359E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -7266,7 +7294,7 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13">
         <f>C2/60</f>
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>25</v>

--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NATIORA\Desktop\S6\MrRojo\TP\SEO\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F308CAA8-6EDA-4DC8-9DE8-0AD6ACA3BA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA34172-347F-4EDE-9D79-C255319728F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,9 +147,6 @@
     <t>Core</t>
   </si>
   <si>
-    <t>mettre en place le strucutre du projet</t>
-  </si>
-  <si>
     <t>orchestration</t>
   </si>
   <si>
@@ -190,6 +187,9 @@
   </si>
   <si>
     <t>Mettre en place le système d'authentifiaction</t>
+  </si>
+  <si>
+    <t>mettre en place la strucutre du projet</t>
   </si>
 </sst>
 </file>
@@ -709,7 +709,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="NATIORA" refreshedDate="46110.462507523145" refreshedVersion="8" recordCount="83" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="NATIORA" refreshedDate="46110.809336226848" refreshedVersion="8" recordCount="83" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K84" sheet="liste des taches"/>
   </cacheSource>
@@ -742,13 +742,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="90"/>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="90"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="90"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="20"/>
     </cacheField>
     <cacheField name="Avancement" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -798,40 +798,40 @@
     <n v="1"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="15"/>
+    <s v="Authentification"/>
+    <s v="Back-office"/>
+    <s v="Inscription dans le site new"/>
+    <s v="SignIn.php"/>
+    <s v="metier"/>
+    <x v="0"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="20"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Authentification"/>
+    <s v="Bakc-office"/>
+    <s v="connexion dans le site new"/>
+    <s v="Login.php"/>
+    <s v="metier"/>
+    <x v="0"/>
     <n v="15"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="15"/>
+    <n v="0"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="15"/>
-    <n v="15"/>
+    <s v="Authentification"/>
+    <s v="Integration"/>
+    <s v="Mettre en place le système d'authentifiaction"/>
+    <s v="Login.php"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="20"/>
     <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="15"/>
-    <n v="15"/>
+    <n v="20"/>
     <n v="0"/>
-    <n v="1"/>
   </r>
   <r>
     <m/>
@@ -3141,13 +3141,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="20" t="s">
@@ -3175,16 +3175,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>16</v>
@@ -3212,19 +3212,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>0</v>
@@ -3233,15 +3233,15 @@
         <v>20</v>
       </c>
       <c r="I5" s="18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J5" s="18">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K5" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
@@ -3249,19 +3249,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>0</v>
@@ -3270,15 +3270,15 @@
         <v>15</v>
       </c>
       <c r="I6" s="18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J6" s="18">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K6" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
@@ -3286,19 +3286,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>49</v>
-      </c>
       <c r="E7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>47</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>48</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>0</v>
@@ -3307,15 +3307,15 @@
         <v>20</v>
       </c>
       <c r="I7" s="18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K7" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
@@ -6201,13 +6201,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="29">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C3" s="30">
         <v>95</v>
       </c>
       <c r="D3" s="31">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
@@ -6215,13 +6215,13 @@
         <v>29</v>
       </c>
       <c r="B4" s="32">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C4" s="33">
         <v>95</v>
       </c>
       <c r="D4" s="34">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1"/>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B12" s="15">
         <f>avancement!D2</f>
-        <v>0.98461538461538467</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7274,15 +7274,15 @@
       </c>
       <c r="B2" s="10">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>3520</v>
+        <v>3575</v>
       </c>
       <c r="C2" s="10">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D2" s="11">
         <f>(B2/(B2+C2))</f>
-        <v>0.98461538461538467</v>
+        <v>1</v>
       </c>
       <c r="E2" s="11">
         <f>((B2+C2)-A2)/A2</f>
@@ -7294,7 +7294,7 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13">
         <f>C2/60</f>
-        <v>0.91666666666666663</v>
+        <v>0</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>25</v>

--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NATIORA\Desktop\S6\MrRojo\TP\SEO\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA34172-347F-4EDE-9D79-C255319728F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E4DBF3-092F-4B4C-975E-E2B427BD7285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
   <si>
     <t>ETU003252</t>
   </si>
@@ -150,9 +150,6 @@
     <t>orchestration</t>
   </si>
   <si>
-    <t>mettre l'environement Docker</t>
-  </si>
-  <si>
     <t>docker-file/docker-yml</t>
   </si>
   <si>
@@ -171,13 +168,7 @@
     <t>Back-office</t>
   </si>
   <si>
-    <t>Inscription dans le site new</t>
-  </si>
-  <si>
     <t>SignIn.php</t>
-  </si>
-  <si>
-    <t>connexion dans le site new</t>
   </si>
   <si>
     <t>Login.php</t>
@@ -190,6 +181,63 @@
   </si>
   <si>
     <t>mettre en place la strucutre du projet</t>
+  </si>
+  <si>
+    <t>mettre en place l'environement Docker</t>
+  </si>
+  <si>
+    <t>Inscription dans le site news</t>
+  </si>
+  <si>
+    <t>connexion dans le site news</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
+  <si>
+    <t>TinyDocs</t>
+  </si>
+  <si>
+    <t>Comprendre le concept de TinyDocs</t>
+  </si>
+  <si>
+    <t>Orientation</t>
+  </si>
+  <si>
+    <t>verifier que la base de donnee  est bien adapter</t>
+  </si>
+  <si>
+    <t>CRUD Article</t>
+  </si>
+  <si>
+    <t>Créer une formulaire pour Ajouter un article (les champs necessaires)</t>
+  </si>
+  <si>
+    <t>create_article.php</t>
+  </si>
+  <si>
+    <t>Integration TinyDocs</t>
+  </si>
+  <si>
+    <t>Ajouter le script CDN et initialiser l'editeur</t>
+  </si>
+  <si>
+    <t>Gerer l'envoi du formulaire</t>
+  </si>
+  <si>
+    <t>affichage</t>
+  </si>
+  <si>
+    <t>dependance</t>
+  </si>
+  <si>
+    <t>Insertion dans la base</t>
+  </si>
+  <si>
+    <t>Persistance</t>
+  </si>
+  <si>
+    <t>generation du slug (amin'ilay SEO)</t>
   </si>
 </sst>
 </file>
@@ -3141,13 +3189,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="20" t="s">
@@ -3181,10 +3229,10 @@
         <v>15</v>
       </c>
       <c r="D4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>16</v>
@@ -3212,19 +3260,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>39</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>0</v>
@@ -3249,19 +3297,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>0</v>
@@ -3286,19 +3334,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>0</v>
@@ -3322,159 +3370,233 @@
       <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
+      <c r="B8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>52</v>
+      </c>
       <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="8"/>
+      <c r="F8" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H8" s="18">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I8" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J8" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K8" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>54</v>
+      </c>
       <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="8"/>
+      <c r="F9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H9" s="18">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I9" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J9" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K9" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="18">
         <v>9</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H10" s="18">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I10" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J10" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K10" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="18">
         <v>10</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H11" s="18">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I11" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J11" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K11" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
       <c r="A12" s="18">
         <v>11</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H12" s="18">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I12" s="8">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J12" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K12" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
       <c r="A13" s="18">
         <v>12</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H13" s="18">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I13" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J13" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K13" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
       <c r="A14" s="18">
         <v>13</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="20"/>
       <c r="G14" s="8"/>
@@ -6237,7 +6359,7 @@
       </c>
       <c r="B12" s="15">
         <f>avancement!D2</f>
-        <v>1</v>
+        <v>0.98104956268221577</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7270,23 +7392,23 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="10">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>3570</v>
+        <v>3425</v>
       </c>
       <c r="B2" s="10">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>3575</v>
+        <v>3365</v>
       </c>
       <c r="C2" s="10">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D2" s="11">
         <f>(B2/(B2+C2))</f>
-        <v>1</v>
+        <v>0.98104956268221577</v>
       </c>
       <c r="E2" s="11">
         <f>((B2+C2)-A2)/A2</f>
-        <v>1.4005602240896359E-3</v>
+        <v>1.4598540145985401E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -7294,7 +7416,7 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13">
         <f>C2/60</f>
-        <v>0</v>
+        <v>1.0833333333333333</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>25</v>

--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NATIORA\Desktop\S6\MrRojo\TP\SEO\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E4DBF3-092F-4B4C-975E-E2B427BD7285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E80E7B1-C9A5-4A40-8CDE-C1B8531E306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
   <si>
     <t>ETU003252</t>
   </si>
@@ -219,9 +219,6 @@
     <t>Integration TinyDocs</t>
   </si>
   <si>
-    <t>Ajouter le script CDN et initialiser l'editeur</t>
-  </si>
-  <si>
     <t>Gerer l'envoi du formulaire</t>
   </si>
   <si>
@@ -234,10 +231,40 @@
     <t>Insertion dans la base</t>
   </si>
   <si>
-    <t>Persistance</t>
+    <t>generation du slug (amin'ilay SEO)</t>
   </si>
   <si>
-    <t>generation du slug (amin'ilay SEO)</t>
+    <t>persistance</t>
+  </si>
+  <si>
+    <t>Front-office</t>
+  </si>
+  <si>
+    <t>Récupérer et afficher l'article</t>
+  </si>
+  <si>
+    <t>article.php</t>
+  </si>
+  <si>
+    <t>Mettre en place URL SEO(ao amin'ilay htaccess)</t>
+  </si>
+  <si>
+    <t>mettre en fin le upload image</t>
+  </si>
+  <si>
+    <t>upload.php</t>
+  </si>
+  <si>
+    <t>Configuration Tinydocs et type Mimme</t>
+  </si>
+  <si>
+    <t>Back-office/Front-office</t>
+  </si>
+  <si>
+    <t>Effectuer un test complet :créer article,checker html dans la base,afficher article,tester les images,tester URL seo</t>
+  </si>
+  <si>
+    <t>Obtenir l'API key,Ajouter le script CDN et initialiser l'editeur</t>
   </si>
 </sst>
 </file>
@@ -348,7 +375,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -463,11 +490,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -519,6 +557,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3453,7 +3492,7 @@
         <v>57</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>0</v>
@@ -3484,13 +3523,13 @@
         <v>41</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>57</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>0</v>
@@ -3521,7 +3560,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>57</v>
@@ -3564,7 +3603,7 @@
         <v>57</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>0</v>
@@ -3594,125 +3633,179 @@
       <c r="C14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="8"/>
+      <c r="D14" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H14" s="18">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="I14" s="8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J14" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K14" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
       <c r="A15" s="18">
         <v>14</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H15" s="18">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I15" s="18">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J15" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K15" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
       <c r="A16" s="18">
         <v>15</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H16" s="18">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I16" s="18">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1">
       <c r="A17" s="18">
         <v>16</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H17" s="18">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I17" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J17" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1">
       <c r="A18" s="18">
         <v>17</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="8"/>
+      <c r="B18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H18" s="18">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I18" s="18">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J18" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K18" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="20"/>
     </row>
@@ -3720,25 +3813,35 @@
       <c r="A19" s="18">
         <v>18</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
+      <c r="B19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>73</v>
+      </c>
       <c r="E19" s="19"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="8"/>
+      <c r="F19" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H19" s="18">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I19" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J19" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K19" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1">
@@ -6359,7 +6462,7 @@
       </c>
       <c r="B12" s="15">
         <f>avancement!D2</f>
-        <v>0.98104956268221577</v>
+        <v>0.95290423861852436</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7392,23 +7495,23 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="10">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>3425</v>
+        <v>3180</v>
       </c>
       <c r="B2" s="10">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>3365</v>
+        <v>3035</v>
       </c>
       <c r="C2" s="10">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D2" s="11">
         <f>(B2/(B2+C2))</f>
-        <v>0.98104956268221577</v>
+        <v>0.95290423861852436</v>
       </c>
       <c r="E2" s="11">
         <f>((B2+C2)-A2)/A2</f>
-        <v>1.4598540145985401E-3</v>
+        <v>1.5723270440251573E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -7416,7 +7519,7 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13">
         <f>C2/60</f>
-        <v>1.0833333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>25</v>

--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NATIORA\Desktop\S6\MrRojo\TP\SEO\SiteActualite\Todo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Etude\S6\Mr_Rojo\Projet\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E80E7B1-C9A5-4A40-8CDE-C1B8531E306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF485AFC-4151-413F-8F58-1D127B1C7EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -19,28 +19,15 @@
     <sheet name="avancement" sheetId="4" r:id="rId4"/>
     <sheet name="detail_avancement" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <pivotCaches>
     <pivotCache cacheId="4" r:id="rId6"/>
   </pivotCaches>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="76">
   <si>
     <t>ETU003252</t>
   </si>
@@ -129,16 +116,10 @@
     <t/>
   </si>
   <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
     <t>Conception</t>
   </si>
   <si>
     <t>Base de donnee</t>
-  </si>
-  <si>
-    <t>faire la conception du projet</t>
   </si>
   <si>
     <t>BDD</t>
@@ -265,6 +246,15 @@
   </si>
   <si>
     <t>Obtenir l'API key,Ajouter le script CDN et initialiser l'editeur</t>
+  </si>
+  <si>
+    <t>Total général</t>
+  </si>
+  <si>
+    <t>faire la conception du projet sans SGBDR</t>
+  </si>
+  <si>
+    <t>faire la conception du projet SGBDR</t>
   </si>
 </sst>
 </file>
@@ -551,13 +541,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,9 +786,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="NATIORA" refreshedDate="46110.809336226848" refreshedVersion="8" recordCount="83" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="ThinkBook" refreshedDate="46111.362069328701" refreshedVersion="8" recordCount="83" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B1:K84" sheet="liste des taches"/>
+    <worksheetSource ref="B1:K86" sheet="liste des taches"/>
   </cacheSource>
   <cacheFields count="10">
     <cacheField name="Catégorie" numFmtId="0">
@@ -826,7 +816,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Estimation" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="90"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="90"/>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="90"/>
@@ -863,7 +853,7 @@
   <r>
     <s v="Structuration"/>
     <s v="Core"/>
-    <s v="mettre en place le strucutre du projet"/>
+    <s v="mettre en place la strucutre du projet"/>
     <m/>
     <s v="setup"/>
     <x v="0"/>
@@ -875,7 +865,7 @@
   <r>
     <s v="orchestration"/>
     <s v="Docker"/>
-    <s v="mettre l'environement Docker"/>
+    <s v="mettre en place l'environement Docker"/>
     <s v="docker-file/docker-yml"/>
     <s v="setup"/>
     <x v="0"/>
@@ -887,26 +877,26 @@
   <r>
     <s v="Authentification"/>
     <s v="Back-office"/>
-    <s v="Inscription dans le site new"/>
+    <s v="Inscription dans le site news"/>
     <s v="SignIn.php"/>
     <s v="metier"/>
     <x v="0"/>
     <n v="20"/>
-    <n v="0"/>
     <n v="20"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Authentification"/>
     <s v="Bakc-office"/>
-    <s v="connexion dans le site new"/>
+    <s v="connexion dans le site news"/>
     <s v="Login.php"/>
     <s v="metier"/>
     <x v="0"/>
     <n v="15"/>
-    <n v="0"/>
     <n v="15"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Authentification"/>
@@ -916,153 +906,153 @@
     <s v="Integration"/>
     <x v="0"/>
     <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Documentation"/>
+    <s v="TinyDocs"/>
+    <s v="Comprendre le concept de TinyDocs"/>
+    <m/>
+    <s v="Orientation"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Conception"/>
+    <s v="Base de donnee"/>
+    <s v="verifier que la base de donnee  est bien adapter"/>
+    <m/>
+    <s v="BDD"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="CRUD Article"/>
+    <s v="Back-office"/>
+    <s v="Créer une formulaire pour Ajouter un article (les champs necessaires)"/>
+    <s v="create_article.php"/>
+    <s v="affichage"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Integration TinyDocs"/>
+    <s v="Back-office"/>
+    <s v="Obtenir l'API key,Ajouter le script CDN et initialiser l'editeur"/>
+    <s v="create_article.php"/>
+    <s v="dependance"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="CRUD Article"/>
+    <s v="Back-office"/>
+    <s v="Gerer l'envoi du formulaire"/>
+    <s v="create_article.php"/>
+    <s v="metier"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="CRUD Article"/>
+    <s v="Back-office"/>
+    <s v="generation du slug (amin'ilay SEO)"/>
+    <s v="create_article.php"/>
+    <s v="metier"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="CRUD Article"/>
+    <s v="Back-office"/>
+    <s v="Insertion dans la base"/>
+    <s v="create_article.php"/>
+    <s v="persistance"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="15"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="CRUD Article"/>
+    <s v="Front-office"/>
+    <s v="Récupérer et afficher l'article"/>
+    <s v="article.php"/>
+    <s v="affichage"/>
+    <x v="0"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="20"/>
     <n v="0"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
+    <s v="CRUD Article"/>
+    <s v="Front-office"/>
+    <s v="Mettre en place URL SEO(ao amin'ilay htaccess)"/>
+    <s v="article.php"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="15"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="15"/>
+    <n v="0"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
+    <s v="CRUD Article"/>
+    <s v="Back-office"/>
+    <s v="mettre en fin le upload image"/>
+    <s v="upload.php"/>
+    <s v="affichage"/>
+    <x v="0"/>
+    <n v="10"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="10"/>
+    <n v="0"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
+    <s v="CRUD Article"/>
+    <s v="Back-office"/>
+    <s v="Configuration Tinydocs et type Mimme"/>
+    <s v="upload.php"/>
+    <s v="metier"/>
+    <x v="0"/>
+    <n v="20"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="20"/>
+    <n v="0"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
+    <s v="CRUD Article"/>
+    <s v="Back-office/Front-office"/>
+    <s v="Effectuer un test complet :créer article,checker html dans la base,afficher article,tester les images,tester URL seo"/>
+    <m/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="5"/>
     <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
+    <n v="5"/>
     <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
   </r>
   <r>
     <m/>
@@ -2112,11 +2102,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B998"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="42.85546875" customWidth="1"/>
-    <col min="3" max="6" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
+    <col min="2" max="2" width="42.86328125" customWidth="1"/>
+    <col min="3" max="6" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1">
@@ -3142,15 +3132,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L1003"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:L1005"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.86328125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="37.1328125" customWidth="1"/>
+    <col min="5" max="5" width="16.3984375" customWidth="1"/>
+    <col min="6" max="6" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1">
@@ -3193,33 +3183,33 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" s="20" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I2" s="18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J2" s="18">
         <f>H2-I2</f>
         <v>0</v>
       </c>
       <c r="K2" s="21">
-        <f t="shared" ref="K2:K84" si="0">I2/(I2+J2)</f>
+        <f t="shared" ref="K2:K86" si="0">I2/(I2+J2)</f>
         <v>1</v>
       </c>
     </row>
@@ -3228,32 +3218,33 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="20" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="18">
+        <v>20</v>
+      </c>
+      <c r="I3" s="18">
+        <v>20</v>
+      </c>
+      <c r="J3" s="18">
+        <f>H3-I3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="18">
-        <v>30</v>
-      </c>
-      <c r="I3" s="18">
-        <v>30</v>
-      </c>
-      <c r="J3" s="18">
-        <v>0</v>
-      </c>
       <c r="K3" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K3" si="1">I3/(I3+J3)</f>
         <v>1</v>
       </c>
     </row>
@@ -3264,15 +3255,13 @@
       <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>15</v>
+      <c r="C4" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>36</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="E4" s="8"/>
       <c r="F4" s="20" t="s">
         <v>16</v>
       </c>
@@ -3280,13 +3269,12 @@
         <v>0</v>
       </c>
       <c r="H4" s="18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I4" s="18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J4" s="18">
-        <f t="shared" ref="J4:J73" si="1">H4-I4</f>
         <v>0</v>
       </c>
       <c r="K4" s="21">
@@ -3299,31 +3287,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="18">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I5" s="18">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J5" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J5:J75" si="2">H5-I5</f>
         <v>0</v>
       </c>
       <c r="K5" s="21">
@@ -3336,31 +3324,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="F6" s="20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H6" s="18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I6" s="18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J6" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K6" s="21">
@@ -3373,31 +3361,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>44</v>
-      </c>
       <c r="D7" s="20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H7" s="18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I7" s="18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J7" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K7" s="21">
@@ -3410,34 +3398,36 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="19"/>
+        <v>43</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="F8" s="20" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="18">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I8" s="18">
+        <v>20</v>
+      </c>
+      <c r="J8" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="J8" s="18">
-        <f t="shared" si="1"/>
-        <v>5</v>
       </c>
       <c r="K8" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
@@ -3445,17 +3435,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="20" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>0</v>
@@ -3464,15 +3454,15 @@
         <v>5</v>
       </c>
       <c r="I9" s="18">
+        <v>5</v>
+      </c>
+      <c r="J9" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="J9" s="18">
-        <f t="shared" si="1"/>
-        <v>5</v>
       </c>
       <c r="K9" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
@@ -3480,36 +3470,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>57</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E10" s="19"/>
       <c r="F10" s="20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="18">
+        <v>5</v>
+      </c>
+      <c r="I10" s="18">
+        <v>5</v>
+      </c>
+      <c r="J10" s="18">
+        <f t="shared" ref="J10" si="3">H10-I10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="18">
-        <v>15</v>
-      </c>
-      <c r="I10" s="18">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
       <c r="K10" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="K10" si="4">I10/(I10+J10)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
@@ -3517,36 +3505,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>57</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E11" s="19"/>
       <c r="F11" s="20" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G11" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="18">
+        <v>5</v>
+      </c>
+      <c r="I11" s="18">
+        <v>5</v>
+      </c>
+      <c r="J11" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="H11" s="18">
-        <v>10</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18">
-        <f t="shared" si="1"/>
-        <v>10</v>
       </c>
       <c r="K11" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
@@ -3554,19 +3540,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>57</v>
-      </c>
       <c r="F12" s="20" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>0</v>
@@ -3574,16 +3560,16 @@
       <c r="H12" s="18">
         <v>15</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="18">
+        <v>15</v>
+      </c>
+      <c r="J12" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="J12" s="18">
-        <f t="shared" si="1"/>
-        <v>15</v>
       </c>
       <c r="K12" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
@@ -3591,36 +3577,36 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>57</v>
-      </c>
       <c r="F13" s="20" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H13" s="18">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I13" s="8">
+        <v>10</v>
+      </c>
+      <c r="J13" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="J13" s="18">
-        <f t="shared" si="1"/>
-        <v>15</v>
       </c>
       <c r="K13" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
@@ -3628,19 +3614,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="F14" s="20" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>0</v>
@@ -3649,15 +3635,15 @@
         <v>15</v>
       </c>
       <c r="I14" s="8">
+        <v>15</v>
+      </c>
+      <c r="J14" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="J14" s="18">
-        <f t="shared" si="1"/>
-        <v>15</v>
       </c>
       <c r="K14" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
@@ -3665,36 +3651,36 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="F15" s="20" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H15" s="18">
-        <v>20</v>
-      </c>
-      <c r="I15" s="18">
+        <v>15</v>
+      </c>
+      <c r="I15" s="8">
+        <v>15</v>
+      </c>
+      <c r="J15" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="J15" s="18">
-        <f t="shared" si="1"/>
-        <v>20</v>
       </c>
       <c r="K15" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
@@ -3702,19 +3688,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="F16" s="20" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>0</v>
@@ -3722,16 +3708,16 @@
       <c r="H16" s="18">
         <v>15</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="8">
+        <v>15</v>
+      </c>
+      <c r="J16" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="J16" s="18">
-        <f t="shared" si="1"/>
-        <v>15</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1">
@@ -3739,32 +3725,32 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="18">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I17" s="18">
         <v>0</v>
       </c>
       <c r="J17" s="18">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="0"/>
@@ -3776,68 +3762,69 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>71</v>
+        <v>63</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>66</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" s="18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I18" s="18">
         <v>0</v>
       </c>
       <c r="J18" s="18">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>15</v>
       </c>
       <c r="K18" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="20"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1">
       <c r="A19" s="18">
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="19"/>
+        <v>67</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="F19" s="20" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I19" s="18">
         <v>0</v>
       </c>
       <c r="J19" s="18">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="K19" s="21">
         <f t="shared" si="0"/>
@@ -3848,80 +3835,113 @@
       <c r="A20" s="18">
         <v>19</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="H20" s="18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I20" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J20" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
       <c r="K20" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1">
       <c r="A21" s="18">
         <v>20</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
+      <c r="B21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>71</v>
+      </c>
       <c r="E21" s="19"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="8"/>
+      <c r="F21" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H21" s="18">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I21" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J21" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="K21" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1">
       <c r="A22" s="18">
         <v>21</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
+      <c r="B22" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>71</v>
+      </c>
       <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="8"/>
+      <c r="F22" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="H22" s="18">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I22" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J22" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J22" si="5">H22-I22</f>
+        <v>5</v>
+      </c>
+      <c r="K22" s="21">
+        <f t="shared" ref="K22" si="6">I22/(I22+J22)</f>
         <v>0</v>
-      </c>
-      <c r="K22" s="21">
-        <f t="shared" si="0"/>
-        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1">
       <c r="A23" s="18">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="20"/>
@@ -3936,7 +3956,7 @@
         <v>30</v>
       </c>
       <c r="J23" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K23" s="21">
@@ -3946,22 +3966,22 @@
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
       <c r="A24" s="18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="8"/>
+      <c r="E24" s="19"/>
       <c r="F24" s="20"/>
       <c r="G24" s="8"/>
       <c r="H24" s="18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I24" s="18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J24" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K24" s="21">
@@ -3971,22 +3991,22 @@
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1">
       <c r="A25" s="18">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
-      <c r="E25" s="8"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="20"/>
       <c r="G25" s="8"/>
       <c r="H25" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I25" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J25" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K25" s="21">
@@ -3996,22 +4016,22 @@
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
       <c r="A26" s="18">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="19"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="20"/>
       <c r="G26" s="8"/>
       <c r="H26" s="18">
-        <v>30</v>
-      </c>
-      <c r="I26" s="8">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="I26" s="18">
+        <v>20</v>
       </c>
       <c r="J26" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K26" s="21">
@@ -4021,22 +4041,22 @@
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1">
       <c r="A27" s="18">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
-      <c r="E27" s="19"/>
+      <c r="E27" s="8"/>
       <c r="F27" s="20"/>
       <c r="G27" s="8"/>
       <c r="H27" s="18">
-        <v>30</v>
-      </c>
-      <c r="I27" s="8">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="I27" s="18">
+        <v>60</v>
       </c>
       <c r="J27" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K27" s="21">
@@ -4046,7 +4066,7 @@
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1">
       <c r="A28" s="18">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="20"/>
@@ -4055,13 +4075,13 @@
       <c r="F28" s="20"/>
       <c r="G28" s="8"/>
       <c r="H28" s="18">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I28" s="8">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J28" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K28" s="21">
@@ -4071,7 +4091,7 @@
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1">
       <c r="A29" s="18">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="20"/>
@@ -4080,13 +4100,13 @@
       <c r="F29" s="20"/>
       <c r="G29" s="8"/>
       <c r="H29" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I29" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J29" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K29" s="21">
@@ -4096,7 +4116,7 @@
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1">
       <c r="A30" s="18">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="20"/>
@@ -4105,13 +4125,13 @@
       <c r="F30" s="20"/>
       <c r="G30" s="8"/>
       <c r="H30" s="18">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="I30" s="8">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="J30" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K30" s="21">
@@ -4121,7 +4141,7 @@
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1">
       <c r="A31" s="18">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="20"/>
@@ -4130,13 +4150,13 @@
       <c r="F31" s="20"/>
       <c r="G31" s="8"/>
       <c r="H31" s="18">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I31" s="8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J31" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K31" s="21">
@@ -4146,7 +4166,7 @@
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1">
       <c r="A32" s="18">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="20"/>
@@ -4161,7 +4181,7 @@
         <v>90</v>
       </c>
       <c r="J32" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K32" s="21">
@@ -4171,7 +4191,7 @@
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="20"/>
@@ -4180,13 +4200,13 @@
       <c r="F33" s="20"/>
       <c r="G33" s="8"/>
       <c r="H33" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I33" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J33" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K33" s="21">
@@ -4196,7 +4216,7 @@
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="18">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="20"/>
@@ -4205,13 +4225,13 @@
       <c r="F34" s="20"/>
       <c r="G34" s="8"/>
       <c r="H34" s="18">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I34" s="8">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J34" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K34" s="21">
@@ -4221,7 +4241,7 @@
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="20"/>
@@ -4230,13 +4250,13 @@
       <c r="F35" s="20"/>
       <c r="G35" s="8"/>
       <c r="H35" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I35" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J35" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K35" s="21">
@@ -4246,11 +4266,11 @@
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1">
       <c r="A36" s="18">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="20"/>
-      <c r="D36" s="19"/>
+      <c r="D36" s="20"/>
       <c r="E36" s="19"/>
       <c r="F36" s="20"/>
       <c r="G36" s="8"/>
@@ -4261,7 +4281,7 @@
         <v>60</v>
       </c>
       <c r="J36" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K36" s="21">
@@ -4271,11 +4291,11 @@
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="20"/>
-      <c r="D37" s="19"/>
+      <c r="D37" s="20"/>
       <c r="E37" s="19"/>
       <c r="F37" s="20"/>
       <c r="G37" s="8"/>
@@ -4286,7 +4306,7 @@
         <v>60</v>
       </c>
       <c r="J37" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K37" s="21">
@@ -4296,7 +4316,7 @@
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="18">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="20"/>
@@ -4311,7 +4331,7 @@
         <v>60</v>
       </c>
       <c r="J38" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K38" s="21">
@@ -4321,11 +4341,11 @@
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1">
       <c r="A39" s="18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
+      <c r="D39" s="19"/>
       <c r="E39" s="19"/>
       <c r="F39" s="20"/>
       <c r="G39" s="8"/>
@@ -4336,7 +4356,7 @@
         <v>60</v>
       </c>
       <c r="J39" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K39" s="21">
@@ -4346,22 +4366,22 @@
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1">
       <c r="A40" s="18">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="8"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="20"/>
       <c r="G40" s="8"/>
       <c r="H40" s="18">
-        <v>30</v>
-      </c>
-      <c r="I40" s="18">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="I40" s="8">
+        <v>60</v>
       </c>
       <c r="J40" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K40" s="21">
@@ -4371,7 +4391,7 @@
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1">
       <c r="A41" s="18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="20"/>
@@ -4380,13 +4400,13 @@
       <c r="F41" s="20"/>
       <c r="G41" s="8"/>
       <c r="H41" s="18">
-        <v>30</v>
-      </c>
-      <c r="I41" s="18">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="I41" s="8">
+        <v>60</v>
       </c>
       <c r="J41" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K41" s="21">
@@ -4396,22 +4416,22 @@
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1">
       <c r="A42" s="18">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
-      <c r="E42" s="19"/>
+      <c r="E42" s="8"/>
       <c r="F42" s="20"/>
       <c r="G42" s="8"/>
       <c r="H42" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I42" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J42" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K42" s="21">
@@ -4421,7 +4441,7 @@
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1">
       <c r="A43" s="18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="20"/>
@@ -4430,13 +4450,13 @@
       <c r="F43" s="20"/>
       <c r="G43" s="8"/>
       <c r="H43" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I43" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J43" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K43" s="21">
@@ -4446,7 +4466,7 @@
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1">
       <c r="A44" s="18">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="20"/>
@@ -4457,11 +4477,11 @@
       <c r="H44" s="18">
         <v>60</v>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="18">
         <v>60</v>
       </c>
       <c r="J44" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K44" s="21">
@@ -4471,7 +4491,7 @@
     </row>
     <row r="45" spans="1:11" ht="15.75" customHeight="1">
       <c r="A45" s="18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="20"/>
@@ -4480,13 +4500,13 @@
       <c r="F45" s="20"/>
       <c r="G45" s="8"/>
       <c r="H45" s="18">
-        <v>90</v>
-      </c>
-      <c r="I45" s="8">
-        <v>90</v>
+        <v>60</v>
+      </c>
+      <c r="I45" s="18">
+        <v>60</v>
       </c>
       <c r="J45" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K45" s="21">
@@ -4496,7 +4516,7 @@
     </row>
     <row r="46" spans="1:11" ht="15.75" customHeight="1">
       <c r="A46" s="18">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="20"/>
@@ -4505,13 +4525,13 @@
       <c r="F46" s="20"/>
       <c r="G46" s="8"/>
       <c r="H46" s="18">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I46" s="8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J46" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K46" s="21">
@@ -4521,22 +4541,22 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" customHeight="1">
       <c r="A47" s="18">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
-      <c r="E47" s="8"/>
+      <c r="E47" s="19"/>
       <c r="F47" s="20"/>
       <c r="G47" s="8"/>
       <c r="H47" s="18">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I47" s="8">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J47" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K47" s="21">
@@ -4546,22 +4566,22 @@
     </row>
     <row r="48" spans="1:11" ht="15.75" customHeight="1">
       <c r="A48" s="18">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
-      <c r="E48" s="8"/>
+      <c r="E48" s="19"/>
       <c r="F48" s="20"/>
       <c r="G48" s="8"/>
       <c r="H48" s="18">
         <v>30</v>
       </c>
-      <c r="I48" s="18">
+      <c r="I48" s="8">
         <v>30</v>
       </c>
       <c r="J48" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K48" s="21">
@@ -4571,7 +4591,7 @@
     </row>
     <row r="49" spans="1:11" ht="15.75" customHeight="1">
       <c r="A49" s="18">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="20"/>
@@ -4580,13 +4600,13 @@
       <c r="F49" s="20"/>
       <c r="G49" s="8"/>
       <c r="H49" s="18">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I49" s="8">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J49" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K49" s="21">
@@ -4596,7 +4616,7 @@
     </row>
     <row r="50" spans="1:11" ht="15.75" customHeight="1">
       <c r="A50" s="18">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="20"/>
@@ -4605,13 +4625,13 @@
       <c r="F50" s="20"/>
       <c r="G50" s="8"/>
       <c r="H50" s="18">
-        <v>45</v>
-      </c>
-      <c r="I50" s="8">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="I50" s="18">
+        <v>30</v>
       </c>
       <c r="J50" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K50" s="21">
@@ -4621,7 +4641,7 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1">
       <c r="A51" s="18">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="20"/>
@@ -4630,13 +4650,13 @@
       <c r="F51" s="20"/>
       <c r="G51" s="8"/>
       <c r="H51" s="18">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I51" s="8">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J51" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K51" s="21">
@@ -4646,7 +4666,7 @@
     </row>
     <row r="52" spans="1:11" ht="15.75" customHeight="1">
       <c r="A52" s="18">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="20"/>
@@ -4657,11 +4677,11 @@
       <c r="H52" s="18">
         <v>45</v>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="8">
         <v>45</v>
       </c>
       <c r="J52" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K52" s="21">
@@ -4671,7 +4691,7 @@
     </row>
     <row r="53" spans="1:11" ht="15.75" customHeight="1">
       <c r="A53" s="18">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="20"/>
@@ -4680,13 +4700,13 @@
       <c r="F53" s="20"/>
       <c r="G53" s="8"/>
       <c r="H53" s="18">
-        <v>30</v>
-      </c>
-      <c r="I53" s="18">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="I53" s="8">
+        <v>60</v>
       </c>
       <c r="J53" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K53" s="21">
@@ -4696,7 +4716,7 @@
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1">
       <c r="A54" s="18">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="20"/>
@@ -4705,13 +4725,13 @@
       <c r="F54" s="20"/>
       <c r="G54" s="8"/>
       <c r="H54" s="18">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I54" s="18">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J54" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K54" s="21">
@@ -4721,7 +4741,7 @@
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1">
       <c r="A55" s="18">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="20"/>
@@ -4736,7 +4756,7 @@
         <v>30</v>
       </c>
       <c r="J55" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K55" s="21">
@@ -4746,7 +4766,7 @@
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1">
       <c r="A56" s="18">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="20"/>
@@ -4761,7 +4781,7 @@
         <v>30</v>
       </c>
       <c r="J56" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K56" s="21">
@@ -4771,7 +4791,7 @@
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1">
       <c r="A57" s="18">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="20"/>
@@ -4780,13 +4800,13 @@
       <c r="F57" s="20"/>
       <c r="G57" s="8"/>
       <c r="H57" s="18">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I57" s="18">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J57" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K57" s="21">
@@ -4796,7 +4816,7 @@
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1">
       <c r="A58" s="18">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="20"/>
@@ -4811,7 +4831,7 @@
         <v>30</v>
       </c>
       <c r="J58" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K58" s="21">
@@ -4821,7 +4841,7 @@
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="18">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="20"/>
@@ -4830,13 +4850,13 @@
       <c r="F59" s="20"/>
       <c r="G59" s="8"/>
       <c r="H59" s="18">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I59" s="18">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J59" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K59" s="21">
@@ -4846,7 +4866,7 @@
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="18">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B60" s="8"/>
       <c r="C60" s="20"/>
@@ -4855,13 +4875,13 @@
       <c r="F60" s="20"/>
       <c r="G60" s="8"/>
       <c r="H60" s="18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I60" s="18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J60" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K60" s="21">
@@ -4871,7 +4891,7 @@
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1">
       <c r="A61" s="18">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B61" s="8"/>
       <c r="C61" s="20"/>
@@ -4880,13 +4900,13 @@
       <c r="F61" s="20"/>
       <c r="G61" s="8"/>
       <c r="H61" s="18">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I61" s="18">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J61" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K61" s="21">
@@ -4896,7 +4916,7 @@
     </row>
     <row r="62" spans="1:11" ht="15.75" customHeight="1">
       <c r="A62" s="18">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="20"/>
@@ -4905,13 +4925,13 @@
       <c r="F62" s="20"/>
       <c r="G62" s="8"/>
       <c r="H62" s="18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I62" s="18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J62" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K62" s="21">
@@ -4921,7 +4941,7 @@
     </row>
     <row r="63" spans="1:11" ht="15.75" customHeight="1">
       <c r="A63" s="18">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="20"/>
@@ -4930,13 +4950,13 @@
       <c r="F63" s="20"/>
       <c r="G63" s="8"/>
       <c r="H63" s="18">
-        <v>60</v>
-      </c>
-      <c r="I63" s="8">
-        <v>60</v>
+        <v>15</v>
+      </c>
+      <c r="I63" s="18">
+        <v>15</v>
       </c>
       <c r="J63" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K63" s="21">
@@ -4946,7 +4966,7 @@
     </row>
     <row r="64" spans="1:11" ht="15.75" customHeight="1">
       <c r="A64" s="18">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="20"/>
@@ -4955,13 +4975,13 @@
       <c r="F64" s="20"/>
       <c r="G64" s="8"/>
       <c r="H64" s="18">
-        <v>60</v>
-      </c>
-      <c r="I64" s="8">
-        <v>60</v>
+        <v>30</v>
+      </c>
+      <c r="I64" s="18">
+        <v>30</v>
       </c>
       <c r="J64" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K64" s="21">
@@ -4971,7 +4991,7 @@
     </row>
     <row r="65" spans="1:11" ht="15.75" customHeight="1">
       <c r="A65" s="18">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="20"/>
@@ -4986,7 +5006,7 @@
         <v>60</v>
       </c>
       <c r="J65" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K65" s="21">
@@ -4996,7 +5016,7 @@
     </row>
     <row r="66" spans="1:11" ht="15.75" customHeight="1">
       <c r="A66" s="18">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="20"/>
@@ -5011,7 +5031,7 @@
         <v>60</v>
       </c>
       <c r="J66" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K66" s="21">
@@ -5021,22 +5041,22 @@
     </row>
     <row r="67" spans="1:11" ht="15.75" customHeight="1">
       <c r="A67" s="18">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B67" s="8"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
       <c r="E67" s="8"/>
-      <c r="F67" s="19"/>
+      <c r="F67" s="20"/>
       <c r="G67" s="8"/>
       <c r="H67" s="18">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I67" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J67" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K67" s="21">
@@ -5046,22 +5066,22 @@
     </row>
     <row r="68" spans="1:11" ht="15.75" customHeight="1">
       <c r="A68" s="18">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B68" s="8"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
       <c r="E68" s="8"/>
-      <c r="F68" s="19"/>
+      <c r="F68" s="20"/>
       <c r="G68" s="8"/>
       <c r="H68" s="18">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I68" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J68" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K68" s="21">
@@ -5071,22 +5091,22 @@
     </row>
     <row r="69" spans="1:11" ht="15.75" customHeight="1">
       <c r="A69" s="18">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
+      <c r="E69" s="8"/>
       <c r="F69" s="19"/>
       <c r="G69" s="8"/>
       <c r="H69" s="18">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I69" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J69" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K69" s="21">
@@ -5096,22 +5116,22 @@
     </row>
     <row r="70" spans="1:11" ht="15.75" customHeight="1">
       <c r="A70" s="18">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="20"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="19"/>
       <c r="G70" s="8"/>
       <c r="H70" s="18">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I70" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J70" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K70" s="21">
@@ -5121,13 +5141,13 @@
     </row>
     <row r="71" spans="1:11" ht="15.75" customHeight="1">
       <c r="A71" s="18">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
       <c r="E71" s="19"/>
-      <c r="F71" s="20"/>
+      <c r="F71" s="19"/>
       <c r="G71" s="8"/>
       <c r="H71" s="18">
         <v>60</v>
@@ -5136,7 +5156,7 @@
         <v>60</v>
       </c>
       <c r="J71" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K71" s="21">
@@ -5146,7 +5166,7 @@
     </row>
     <row r="72" spans="1:11" ht="15.75" customHeight="1">
       <c r="A72" s="18">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="19"/>
@@ -5161,7 +5181,7 @@
         <v>60</v>
       </c>
       <c r="J72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K72" s="21">
@@ -5171,7 +5191,7 @@
     </row>
     <row r="73" spans="1:11" ht="15.75" customHeight="1">
       <c r="A73" s="18">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="19"/>
@@ -5186,7 +5206,7 @@
         <v>60</v>
       </c>
       <c r="J73" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K73" s="21">
@@ -5196,21 +5216,22 @@
     </row>
     <row r="74" spans="1:11" ht="15.75" customHeight="1">
       <c r="A74" s="18">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B74" s="8"/>
-      <c r="C74" s="20"/>
+      <c r="C74" s="19"/>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
+      <c r="F74" s="20"/>
       <c r="G74" s="8"/>
       <c r="H74" s="18">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I74" s="8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J74" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K74" s="21">
@@ -5220,21 +5241,22 @@
     </row>
     <row r="75" spans="1:11" ht="15.75" customHeight="1">
       <c r="A75" s="18">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B75" s="8"/>
-      <c r="C75" s="20"/>
+      <c r="C75" s="19"/>
       <c r="D75" s="19"/>
       <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
+      <c r="F75" s="20"/>
       <c r="G75" s="8"/>
       <c r="H75" s="18">
         <v>60</v>
       </c>
       <c r="I75" s="8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J75" s="18">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K75" s="21">
@@ -5244,7 +5266,7 @@
     </row>
     <row r="76" spans="1:11" ht="15.75" customHeight="1">
       <c r="A76" s="18">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="20"/>
@@ -5259,7 +5281,6 @@
         <v>30</v>
       </c>
       <c r="J76" s="18">
-        <f>H76-I76</f>
         <v>0</v>
       </c>
       <c r="K76" s="21">
@@ -5269,7 +5290,7 @@
     </row>
     <row r="77" spans="1:11" ht="15.75" customHeight="1">
       <c r="A77" s="18">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="20"/>
@@ -5278,10 +5299,10 @@
       <c r="F77" s="19"/>
       <c r="G77" s="8"/>
       <c r="H77" s="18">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I77" s="8">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="J77" s="18">
         <v>0</v>
@@ -5293,7 +5314,7 @@
     </row>
     <row r="78" spans="1:11" ht="15.75" customHeight="1">
       <c r="A78" s="18">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="20"/>
@@ -5308,6 +5329,7 @@
         <v>30</v>
       </c>
       <c r="J78" s="18">
+        <f>H78-I78</f>
         <v>0</v>
       </c>
       <c r="K78" s="21">
@@ -5317,7 +5339,7 @@
     </row>
     <row r="79" spans="1:11" ht="15.75" customHeight="1">
       <c r="A79" s="18">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="20"/>
@@ -5326,10 +5348,10 @@
       <c r="F79" s="19"/>
       <c r="G79" s="8"/>
       <c r="H79" s="18">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I79" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J79" s="18">
         <v>0</v>
@@ -5341,7 +5363,7 @@
     </row>
     <row r="80" spans="1:11" ht="15.75" customHeight="1">
       <c r="A80" s="18">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B80" s="8"/>
       <c r="C80" s="20"/>
@@ -5350,10 +5372,10 @@
       <c r="F80" s="19"/>
       <c r="G80" s="8"/>
       <c r="H80" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I80" s="8">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J80" s="18">
         <v>0</v>
@@ -5365,7 +5387,7 @@
     </row>
     <row r="81" spans="1:11" ht="15.75" customHeight="1">
       <c r="A81" s="18">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B81" s="8"/>
       <c r="C81" s="20"/>
@@ -5374,10 +5396,10 @@
       <c r="F81" s="19"/>
       <c r="G81" s="8"/>
       <c r="H81" s="18">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I81" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J81" s="18">
         <v>0</v>
@@ -5389,7 +5411,7 @@
     </row>
     <row r="82" spans="1:11" ht="15.75" customHeight="1">
       <c r="A82" s="18">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B82" s="8"/>
       <c r="C82" s="20"/>
@@ -5398,10 +5420,10 @@
       <c r="F82" s="19"/>
       <c r="G82" s="8"/>
       <c r="H82" s="18">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I82" s="8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J82" s="18">
         <v>0</v>
@@ -5413,10 +5435,10 @@
     </row>
     <row r="83" spans="1:11" ht="15.75" customHeight="1">
       <c r="A83" s="18">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B83" s="8"/>
-      <c r="C83" s="19"/>
+      <c r="C83" s="20"/>
       <c r="D83" s="19"/>
       <c r="E83" s="19"/>
       <c r="F83" s="19"/>
@@ -5437,10 +5459,10 @@
     </row>
     <row r="84" spans="1:11" ht="15.75" customHeight="1">
       <c r="A84" s="18">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B84" s="8"/>
-      <c r="C84" s="19"/>
+      <c r="C84" s="20"/>
       <c r="D84" s="19"/>
       <c r="E84" s="19"/>
       <c r="F84" s="19"/>
@@ -5459,8 +5481,54 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="86" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="85" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A85" s="18">
+        <v>82</v>
+      </c>
+      <c r="B85" s="8"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="18">
+        <v>30</v>
+      </c>
+      <c r="I85" s="8">
+        <v>30</v>
+      </c>
+      <c r="J85" s="18">
+        <v>0</v>
+      </c>
+      <c r="K85" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A86" s="18">
+        <v>83</v>
+      </c>
+      <c r="B86" s="8"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="19"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="18">
+        <v>30</v>
+      </c>
+      <c r="I86" s="8">
+        <v>30</v>
+      </c>
+      <c r="J86" s="18">
+        <v>0</v>
+      </c>
+      <c r="K86" s="21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
     <row r="87" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="88" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="89" spans="1:11" ht="15.75" customHeight="1"/>
@@ -6378,6 +6446,8 @@
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
     <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -6390,13 +6460,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
-    <col min="5" max="6" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" customWidth="1"/>
+    <col min="4" max="4" width="19.3984375" customWidth="1"/>
+    <col min="5" max="6" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
@@ -6425,28 +6495,28 @@
       <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="30">
+        <v>300</v>
+      </c>
+      <c r="C3" s="31">
         <v>150</v>
       </c>
-      <c r="C3" s="30">
-        <v>95</v>
-      </c>
-      <c r="D3" s="31">
-        <v>55</v>
+      <c r="D3" s="32">
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="32">
+        <v>73</v>
+      </c>
+      <c r="B4" s="33">
+        <v>300</v>
+      </c>
+      <c r="C4" s="34">
         <v>150</v>
       </c>
-      <c r="C4" s="33">
-        <v>95</v>
-      </c>
-      <c r="D4" s="34">
-        <v>55</v>
+      <c r="D4" s="35">
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1"/>
@@ -6462,7 +6532,7 @@
       </c>
       <c r="B12" s="15">
         <f>avancement!D2</f>
-        <v>0.95290423861852436</v>
+        <v>0.976303317535545</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7465,14 +7535,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.73046875" customWidth="1"/>
+    <col min="2" max="2" width="17.86328125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.265625" customWidth="1"/>
+    <col min="5" max="5" width="13.73046875" customWidth="1"/>
+    <col min="6" max="6" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
@@ -7495,23 +7565,23 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="10">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>3180</v>
+        <v>3160</v>
       </c>
       <c r="B2" s="10">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>3035</v>
+        <v>3090</v>
       </c>
       <c r="C2" s="10">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D2" s="11">
         <f>(B2/(B2+C2))</f>
-        <v>0.95290423861852436</v>
+        <v>0.976303317535545</v>
       </c>
       <c r="E2" s="11">
         <f>((B2+C2)-A2)/A2</f>
-        <v>1.5723270440251573E-3</v>
+        <v>1.5822784810126582E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -7519,7 +7589,7 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13">
         <f>C2/60</f>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>25</v>
@@ -8535,9 +8605,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="7" width="12.5703125" customWidth="1"/>
+    <col min="1" max="7" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1">

--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Etude\S6\Mr_Rojo\Projet\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF485AFC-4151-413F-8F58-1D127B1C7EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855D84BE-2085-4936-B5C0-F8FB4208AAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
   <si>
     <t>ETU003252</t>
   </si>
@@ -256,6 +256,18 @@
   <si>
     <t>faire la conception du projet SGBDR</t>
   </si>
+  <si>
+    <t xml:space="preserve">Optimisation du site </t>
+  </si>
+  <si>
+    <t>Optimisation</t>
+  </si>
+  <si>
+    <t>Recherche article mulit-critere</t>
+  </si>
+  <si>
+    <t>Doc-technique</t>
+  </si>
 </sst>
 </file>
 
@@ -365,7 +377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -491,11 +503,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -545,6 +575,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -786,7 +820,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="ThinkBook" refreshedDate="46111.362069328701" refreshedVersion="8" recordCount="83" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="ThinkBook" refreshedDate="46111.484902314813" refreshedVersion="8" recordCount="85" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K86" sheet="liste des taches"/>
   </cacheSource>
@@ -809,8 +843,8 @@
     <cacheField name="Qui" numFmtId="0">
       <sharedItems containsBlank="1" count="5">
         <s v="ETU003252"/>
+        <s v="ETU003777"/>
         <m/>
-        <s v="ETU003777" u="1"/>
         <s v="ETU003329" u="1"/>
         <s v="ETU003289" u="1"/>
       </sharedItems>
@@ -822,7 +856,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="90"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="20"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="60"/>
     </cacheField>
     <cacheField name="Avancement" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
@@ -837,16 +871,28 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="83">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="85">
   <r>
     <s v="Conception"/>
     <s v="Base de donnee"/>
-    <s v="faire la conception du projet"/>
+    <s v="faire la conception du projet sans SGBDR"/>
     <m/>
     <s v="BDD"/>
     <x v="0"/>
-    <n v="40"/>
-    <n v="40"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Conception"/>
+    <s v="Base de donnee"/>
+    <s v="faire la conception du projet SGBDR"/>
+    <m/>
+    <s v="BDD"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -868,7 +914,7 @@
     <s v="mettre en place l'environement Docker"/>
     <s v="docker-file/docker-yml"/>
     <s v="setup"/>
-    <x v="0"/>
+    <x v="1"/>
     <n v="25"/>
     <n v="25"/>
     <n v="0"/>
@@ -918,9 +964,21 @@
     <s v="Orientation"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="0"/>
     <n v="5"/>
     <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Documentation"/>
+    <s v="TinyDocs"/>
+    <s v="Comprendre le concept de TinyDocs"/>
+    <m/>
+    <s v="Orientation"/>
+    <x v="1"/>
+    <n v="5"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Conception"/>
@@ -928,11 +986,11 @@
     <s v="verifier que la base de donnee  est bien adapter"/>
     <m/>
     <s v="BDD"/>
-    <x v="0"/>
+    <x v="1"/>
+    <n v="5"/>
     <n v="5"/>
     <n v="0"/>
-    <n v="5"/>
-    <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="CRUD Article"/>
@@ -942,9 +1000,9 @@
     <s v="affichage"/>
     <x v="0"/>
     <n v="15"/>
-    <n v="0"/>
     <n v="15"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="Integration TinyDocs"/>
@@ -954,9 +1012,9 @@
     <s v="dependance"/>
     <x v="0"/>
     <n v="10"/>
-    <n v="0"/>
     <n v="10"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="CRUD Article"/>
@@ -966,9 +1024,9 @@
     <s v="metier"/>
     <x v="0"/>
     <n v="15"/>
-    <n v="0"/>
     <n v="15"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="CRUD Article"/>
@@ -978,9 +1036,9 @@
     <s v="metier"/>
     <x v="0"/>
     <n v="15"/>
-    <n v="0"/>
     <n v="15"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="CRUD Article"/>
@@ -990,9 +1048,9 @@
     <s v="persistance"/>
     <x v="0"/>
     <n v="15"/>
-    <n v="0"/>
     <n v="15"/>
     <n v="0"/>
+    <n v="1"/>
   </r>
   <r>
     <s v="CRUD Article"/>
@@ -1000,7 +1058,7 @@
     <s v="Récupérer et afficher l'article"/>
     <s v="article.php"/>
     <s v="affichage"/>
-    <x v="0"/>
+    <x v="1"/>
     <n v="20"/>
     <n v="0"/>
     <n v="20"/>
@@ -1013,9 +1071,9 @@
     <s v="article.php"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="15"/>
+    <n v="30"/>
     <n v="0"/>
-    <n v="15"/>
+    <n v="30"/>
     <n v="0"/>
   </r>
   <r>
@@ -1024,7 +1082,7 @@
     <s v="mettre en fin le upload image"/>
     <s v="upload.php"/>
     <s v="affichage"/>
-    <x v="0"/>
+    <x v="1"/>
     <n v="10"/>
     <n v="0"/>
     <n v="10"/>
@@ -1036,7 +1094,7 @@
     <s v="Configuration Tinydocs et type Mimme"/>
     <s v="upload.php"/>
     <s v="metier"/>
-    <x v="0"/>
+    <x v="1"/>
     <n v="20"/>
     <n v="0"/>
     <n v="20"/>
@@ -1055,11 +1113,35 @@
     <n v="0"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="CRUD Article"/>
+    <s v="Back-office/Front-office"/>
+    <s v="Effectuer un test complet :créer article,checker html dans la base,afficher article,tester les images,tester URL seo"/>
+    <m/>
+    <s v="Integration"/>
+    <x v="1"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Optimisation"/>
+    <s v="Back-office/Front-office"/>
+    <s v="Optimisation du site "/>
+    <m/>
+    <s v="Optimisation"/>
+    <x v="1"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="60"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="CRUD Article"/>
+    <s v="Recherche article mulit-critere"/>
+    <m/>
+    <s v="article.php"/>
+    <s v="metier"/>
     <x v="1"/>
     <n v="30"/>
     <n v="30"/>
@@ -1067,12 +1149,12 @@
     <n v="1"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
+    <s v="Documentation"/>
+    <s v="Doc-technique"/>
+    <m/>
+    <m/>
+    <s v="Documentation"/>
+    <x v="0"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1084,7 +1166,31 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1096,7 +1202,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1108,7 +1214,391 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
+    <n v="35"/>
+    <n v="35"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="50"/>
+    <n v="50"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
     <n v="20"/>
     <n v="20"/>
     <n v="0"/>
@@ -1120,7 +1610,31 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
     <n v="60"/>
     <n v="60"/>
     <n v="0"/>
@@ -1132,7 +1646,127 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1144,7 +1778,19 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
+    <n v="60"/>
+    <n v="65"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1156,9 +1802,9 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
-    <n v="35"/>
-    <n v="35"/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1168,7 +1814,31 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
     <n v="60"/>
     <n v="60"/>
     <n v="0"/>
@@ -1180,43 +1850,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="50"/>
-    <n v="50"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1228,79 +1862,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1312,7 +1874,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1324,511 +1886,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="45"/>
-    <n v="45"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="45"/>
-    <n v="45"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="45"/>
-    <n v="45"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="90"/>
-    <n v="90"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="20"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="15"/>
-    <n v="15"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="20"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="20"/>
-    <n v="20"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="65"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="15"/>
-    <n v="15"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="60"/>
-    <n v="60"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <n v="30"/>
-    <n v="30"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="30"/>
     <n v="30"/>
     <n v="0"/>
@@ -1839,7 +1897,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="" updatedVersion="8" compact="0" compactData="0">
-  <location ref="A1:D4" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="A1:D5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -1851,8 +1909,8 @@
         <item x="0"/>
         <item h="1" m="1" x="4"/>
         <item h="1" m="1" x="3"/>
-        <item m="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1864,9 +1922,12 @@
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="3">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -3138,7 +3199,7 @@
     <col min="1" max="1" width="5.86328125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="37.1328125" customWidth="1"/>
+    <col min="4" max="4" width="38.46484375" customWidth="1"/>
     <col min="5" max="5" width="16.3984375" customWidth="1"/>
     <col min="6" max="6" width="12.59765625" customWidth="1"/>
   </cols>
@@ -3703,7 +3764,7 @@
         <v>62</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="18">
         <v>15</v>
@@ -3777,17 +3838,17 @@
         <v>42</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" s="18">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I18" s="18">
         <v>0</v>
       </c>
       <c r="J18" s="18">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K18" s="21">
         <f t="shared" si="0"/>
@@ -3943,37 +4004,56 @@
       <c r="A23" s="18">
         <v>20</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
+      <c r="B23" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>76</v>
+      </c>
       <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="8"/>
+      <c r="F23" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="H23" s="18">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I23" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J23" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K23" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
       <c r="A24" s="18">
         <v>21</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="20"/>
+      <c r="B24" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>78</v>
+      </c>
       <c r="D24" s="20"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="8"/>
+      <c r="E24" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="H24" s="18">
         <v>30</v>
       </c>
@@ -3993,32 +4073,40 @@
       <c r="A25" s="18">
         <v>22</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="20"/>
+      <c r="B25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>79</v>
+      </c>
       <c r="D25" s="20"/>
       <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="8"/>
+      <c r="F25" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>0</v>
+      </c>
       <c r="H25" s="18">
         <v>30</v>
       </c>
       <c r="I25" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J25" s="18">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K25" s="21">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
       <c r="A26" s="18">
         <v>23</v>
       </c>
-      <c r="B26" s="8"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
       <c r="E26" s="8"/>
@@ -6496,30 +6584,43 @@
         <v>0</v>
       </c>
       <c r="B3" s="30">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="C3" s="31">
+        <v>210</v>
+      </c>
+      <c r="D3" s="32">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="34">
+        <v>200</v>
+      </c>
+      <c r="C4" s="35">
+        <v>85</v>
+      </c>
+      <c r="D4" s="36">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="37">
+        <v>445</v>
+      </c>
+      <c r="C5" s="38">
+        <v>295</v>
+      </c>
+      <c r="D5" s="39">
         <v>150</v>
       </c>
-      <c r="D3" s="32">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="33">
-        <v>300</v>
-      </c>
-      <c r="C4" s="34">
-        <v>150</v>
-      </c>
-      <c r="D4" s="35">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1"/>
+    </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="7" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="8" spans="1:4" ht="15.75" customHeight="1"/>
@@ -6532,7 +6633,7 @@
       </c>
       <c r="B12" s="15">
         <f>avancement!D2</f>
-        <v>0.976303317535545</v>
+        <v>0.94392523364485981</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7565,23 +7666,23 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="10">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>3160</v>
+        <v>3205</v>
       </c>
       <c r="B2" s="10">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>3090</v>
+        <v>3030</v>
       </c>
       <c r="C2" s="10">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="D2" s="11">
         <f>(B2/(B2+C2))</f>
-        <v>0.976303317535545</v>
+        <v>0.94392523364485981</v>
       </c>
       <c r="E2" s="11">
         <f>((B2+C2)-A2)/A2</f>
-        <v>1.5822784810126582E-3</v>
+        <v>1.5600624024960999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -7589,7 +7690,7 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13">
         <f>C2/60</f>
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>25</v>

--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Etude\S6\Mr_Rojo\Projet\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855D84BE-2085-4936-B5C0-F8FB4208AAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B0D9A7-8050-4794-A220-655825485E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="82">
   <si>
     <t>ETU003252</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>Doc-technique</t>
+  </si>
+  <si>
+    <t>Gestion des artciles</t>
+  </si>
+  <si>
+    <t>crud_article.php</t>
   </si>
 </sst>
 </file>
@@ -4106,12 +4112,24 @@
       <c r="A26" s="18">
         <v>23</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="8"/>
+      <c r="B26" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="H26" s="18">
         <v>20</v>
       </c>

--- a/Todo/To_Site_News.xlsx
+++ b/Todo/To_Site_News.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Etude\S6\Mr_Rojo\Projet\SiteActualite\Todo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B0D9A7-8050-4794-A220-655825485E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659F1AE8-3D5A-482A-8DFF-352BB0EF374D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="84">
   <si>
     <t>ETU003252</t>
   </si>
@@ -273,6 +273,12 @@
   </si>
   <si>
     <t>crud_article.php</t>
+  </si>
+  <si>
+    <t>Responsivite</t>
+  </si>
+  <si>
+    <t>Responsivite mobile</t>
   </si>
 </sst>
 </file>
@@ -3813,15 +3819,15 @@
         <v>20</v>
       </c>
       <c r="I17" s="18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J17" s="18">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1">
@@ -3850,15 +3856,15 @@
         <v>30</v>
       </c>
       <c r="I18" s="18">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J18" s="18">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K18" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1">
@@ -3887,15 +3893,15 @@
         <v>10</v>
       </c>
       <c r="I19" s="18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J19" s="18">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K19" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1">
@@ -4030,14 +4036,14 @@
         <v>60</v>
       </c>
       <c r="I23" s="18">
+        <v>60</v>
+      </c>
+      <c r="J23" s="18">
         <v>0</v>
-      </c>
-      <c r="J23" s="18">
-        <v>60</v>
       </c>
       <c r="K23" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
@@ -4149,17 +4155,27 @@
       <c r="A27" s="18">
         <v>24</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
+      <c r="B27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>83</v>
+      </c>
       <c r="E27" s="8"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="8"/>
+      <c r="F27" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="H27" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I27" s="18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J27" s="18">
         <f t="shared" si="2"/>
@@ -6651,7 +6667,7 @@
       </c>
       <c r="B12" s="15">
         <f>avancement!D2</f>
-        <v>0.94392523364485981</v>
+        <v>0.98113207547169812</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7684,23 +7700,23 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="10">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>3205</v>
+        <v>3175</v>
       </c>
       <c r="B2" s="10">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>3030</v>
+        <v>3120</v>
       </c>
       <c r="C2" s="10">
         <f>SUM('liste des taches'!J:J)</f>
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="D2" s="11">
         <f>(B2/(B2+C2))</f>
-        <v>0.94392523364485981</v>
+        <v>0.98113207547169812</v>
       </c>
       <c r="E2" s="11">
         <f>((B2+C2)-A2)/A2</f>
-        <v>1.5600624024960999E-3</v>
+        <v>1.5748031496062992E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
@@ -7708,7 +7724,7 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13">
         <f>C2/60</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>25</v>
